--- a/data-source/settlements-climate-master.xlsx
+++ b/data-source/settlements-climate-master.xlsx
@@ -438,18 +438,18 @@
     <col width="17" customWidth="1" min="5" max="5"/>
     <col width="13" customWidth="1" min="6" max="6"/>
     <col width="10" customWidth="1" min="7" max="7"/>
-    <col width="32" customWidth="1" min="8" max="8"/>
+    <col width="40" customWidth="1" min="8" max="8"/>
     <col width="23" customWidth="1" min="9" max="9"/>
     <col width="13" customWidth="1" min="10" max="10"/>
     <col width="10" customWidth="1" min="11" max="11"/>
-    <col width="18" customWidth="1" min="12" max="12"/>
+    <col width="40" customWidth="1" min="12" max="12"/>
     <col width="23" customWidth="1" min="13" max="13"/>
     <col width="12" customWidth="1" min="14" max="14"/>
     <col width="18" customWidth="1" min="15" max="15"/>
-    <col width="18" customWidth="1" min="16" max="16"/>
+    <col width="40" customWidth="1" min="16" max="16"/>
     <col width="23" customWidth="1" min="17" max="17"/>
     <col width="16" customWidth="1" min="18" max="18"/>
-    <col width="16" customWidth="1" min="19" max="19"/>
+    <col width="40" customWidth="1" min="19" max="19"/>
     <col width="23" customWidth="1" min="20" max="20"/>
     <col width="22" customWidth="1" min="21" max="21"/>
     <col width="22" customWidth="1" min="22" max="22"/>
@@ -627,42 +627,61 @@
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>СП 20.13330.2016, приложение К</t>
+          <t>СП 20.13330.2016 / СП 14.13330; сверено через ese.pro/tools/calculatory/klimaticheskie-nagruzki/</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>from_sp20_appendix_k</t>
-        </is>
+          <t>verified</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>I</t>
+        </is>
+      </c>
+      <c r="K2" t="n">
+        <v>0.23</v>
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>СП 20.13330.2016</t>
+          <t>СП 20.13330.2016 / СП 14.13330; сверено через ese.pro/tools/calculatory/klimaticheskie-nagruzki/</t>
         </is>
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>requires_verification</t>
-        </is>
+          <t>verified</t>
+        </is>
+      </c>
+      <c r="N2" t="inlineStr">
+        <is>
+          <t>II</t>
+        </is>
+      </c>
+      <c r="O2" t="n">
+        <v>5</v>
       </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>СП 20.13330.2016</t>
+          <t>СП 20.13330.2016 / СП 14.13330; сверено через ese.pro/tools/calculatory/klimaticheskie-nagruzki/</t>
         </is>
       </c>
       <c r="Q2" t="inlineStr">
         <is>
-          <t>requires_verification</t>
-        </is>
+          <t>verified</t>
+        </is>
+      </c>
+      <c r="R2" t="n">
+        <v>5</v>
       </c>
       <c r="S2" t="inlineStr">
         <is>
-          <t>СП 14.13330</t>
+          <t>СП 20.13330.2016 / СП 14.13330; сверено через ese.pro/tools/calculatory/klimaticheskie-nagruzki/</t>
         </is>
       </c>
       <c r="T2" t="inlineStr">
         <is>
-          <t>requires_verification</t>
+          <t>verified</t>
         </is>
       </c>
       <c r="V2" t="inlineStr">
@@ -678,12 +697,12 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>partial</t>
+          <t>verified</t>
         </is>
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>Контрольный город. Снег по прил. К СП 20.13330.2016.</t>
+          <t>Контрольный город. Все параметры сверены через ese.pro/tools/calculatory/klimaticheskie-nagruzki/. Снеговая по прил. К СП 20.13330.2016: район III, Sg=1.5 кПа (в калькуляторе ese.pro показывается уточнённое значение 1.45 кПа). Ветровая I (0.23 кПа), гололёдная II (5 мм). Сейсмика по ОСР-2015 (карты A/B/C по СП 14.13330): 5 баллов.</t>
         </is>
       </c>
     </row>
@@ -18615,14 +18634,33 @@
       <c r="D2" t="n">
         <v>1.5</v>
       </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>I</t>
+        </is>
+      </c>
+      <c r="F2" t="n">
+        <v>0.23</v>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>II</t>
+        </is>
+      </c>
+      <c r="H2" t="n">
+        <v>5</v>
+      </c>
+      <c r="I2" t="n">
+        <v>5</v>
+      </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>partial</t>
+          <t>verified</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>Контрольный город. Снег по прил. К СП 20.13330.2016.</t>
+          <t>Контрольный город. Все параметры сверены через ese.pro/tools/calculatory/klimaticheskie-nagruzki/. Снеговая по прил. К СП 20.13330.2016: район III, Sg=1.5 кПа (в калькуляторе ese.pro показывается уточнённое значение 1.45 кПа). Ветровая I (0.23 кПа), гололёдная II (5 мм). Сейсмика по ОСР-2015 (карты A/B/C по СП 14.13330): 5 баллов.</t>
         </is>
       </c>
     </row>

--- a/data-source/settlements-climate-master.xlsx
+++ b/data-source/settlements-climate-master.xlsx
@@ -624,7 +624,7 @@
         </is>
       </c>
       <c r="G2" t="n">
-        <v>1.5</v>
+        <v>1.45</v>
       </c>
       <c r="H2" t="inlineStr">
         <is>
@@ -739,7 +739,7 @@
         </is>
       </c>
       <c r="G3" t="n">
-        <v>1.5</v>
+        <v>1.3</v>
       </c>
       <c r="H3" t="inlineStr">
         <is>
@@ -818,7 +818,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>Контрольный город. Снег по прил. К СП 20.13330.2016. Sg уточнённое ese.pro: 1.3 кПа</t>
+          <t>Контрольный город. Снег по прил. К СП 20.13330.2016.</t>
         </is>
       </c>
     </row>
@@ -854,7 +854,7 @@
         </is>
       </c>
       <c r="G4" t="n">
-        <v>1.5</v>
+        <v>1.2</v>
       </c>
       <c r="H4" t="inlineStr">
         <is>
@@ -933,7 +933,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>Контрольный город. Базовая запись из ТЗ. Sg уточнённое ese.pro: 1.2 кПа</t>
+          <t>Контрольный город. Базовая запись из ТЗ.</t>
         </is>
       </c>
     </row>
@@ -969,7 +969,7 @@
         </is>
       </c>
       <c r="G5" t="n">
-        <v>1.5</v>
+        <v>1.35</v>
       </c>
       <c r="H5" t="inlineStr">
         <is>
@@ -1048,7 +1048,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>Контрольный город. Снег по прил. К СП 20.13330.2016. Sg уточнённое ese.pro: 1.35 кПа</t>
+          <t>Контрольный город. Снег по прил. К СП 20.13330.2016.</t>
         </is>
       </c>
     </row>
@@ -1084,7 +1084,7 @@
         </is>
       </c>
       <c r="G6" t="n">
-        <v>2.5</v>
+        <v>2.3</v>
       </c>
       <c r="H6" t="inlineStr">
         <is>
@@ -1163,7 +1163,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>Контрольный город. Снег по прил. К СП 20.13330.2016. Sg уточнённое ese.pro: 2.3 кПа</t>
+          <t>Контрольный город. Снег по прил. К СП 20.13330.2016.</t>
         </is>
       </c>
     </row>
@@ -1199,7 +1199,7 @@
         </is>
       </c>
       <c r="G7" t="n">
-        <v>2</v>
+        <v>1.6</v>
       </c>
       <c r="H7" t="inlineStr">
         <is>
@@ -1278,7 +1278,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>Контрольный город. Снег по прил. К СП 20.13330.2016. Sg уточнённое ese.pro: 1.6 кПа</t>
+          <t>Контрольный город. Снег по прил. К СП 20.13330.2016.</t>
         </is>
       </c>
     </row>
@@ -1314,7 +1314,7 @@
         </is>
       </c>
       <c r="G8" t="n">
-        <v>1.5</v>
+        <v>1.1</v>
       </c>
       <c r="H8" t="inlineStr">
         <is>
@@ -1393,7 +1393,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>Контрольный город. Снег по прил. К СП 20.13330.2016. Sg уточнённое ese.pro: 1.1 кПа</t>
+          <t>Контрольный город. Снег по прил. К СП 20.13330.2016.</t>
         </is>
       </c>
     </row>
@@ -1429,7 +1429,7 @@
         </is>
       </c>
       <c r="G9" t="n">
-        <v>2</v>
+        <v>1.95</v>
       </c>
       <c r="H9" t="inlineStr">
         <is>
@@ -1508,7 +1508,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>Контрольный город. Снег по прил. К СП 20.13330.2016. Sg уточнённое ese.pro: 1.95 кПа</t>
+          <t>Контрольный город. Снег по прил. К СП 20.13330.2016.</t>
         </is>
       </c>
     </row>
@@ -1544,7 +1544,7 @@
         </is>
       </c>
       <c r="G10" t="n">
-        <v>2.5</v>
+        <v>2.45</v>
       </c>
       <c r="H10" t="inlineStr">
         <is>
@@ -1623,7 +1623,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>Контрольный город. Снег по прил. К СП 20.13330.2016 — требует сверки (граница IV/V). Sg уточнённое ese.pro: 2.45 кПа</t>
+          <t>Контрольный город. Снег по прил. К СП 20.13330.2016 — требует сверки (граница IV/V).</t>
         </is>
       </c>
     </row>
@@ -1659,7 +1659,7 @@
         </is>
       </c>
       <c r="G11" t="n">
-        <v>2</v>
+        <v>1.6</v>
       </c>
       <c r="H11" t="inlineStr">
         <is>
@@ -1738,7 +1738,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>Контрольный город. Снег по прил. К СП 20.13330.2016. Sg уточнённое ese.pro: 1.6 кПа</t>
+          <t>Контрольный город. Снег по прил. К СП 20.13330.2016.</t>
         </is>
       </c>
     </row>
@@ -1774,7 +1774,7 @@
         </is>
       </c>
       <c r="G12" t="n">
-        <v>1</v>
+        <v>0.85</v>
       </c>
       <c r="H12" t="inlineStr">
         <is>
@@ -1853,7 +1853,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>Контрольный город. Снег по прил. К СП 20.13330.2016. Sg уточнённое ese.pro: 0.85 кПа</t>
+          <t>Контрольный город. Снег по прил. К СП 20.13330.2016.</t>
         </is>
       </c>
     </row>
@@ -1889,7 +1889,7 @@
         </is>
       </c>
       <c r="G13" t="n">
-        <v>2</v>
+        <v>1.6</v>
       </c>
       <c r="H13" t="inlineStr">
         <is>
@@ -1968,7 +1968,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>Контрольный город. Снег по прил. К СП 20.13330.2016. Sg уточнённое ese.pro: 1.6 кПа</t>
+          <t>Контрольный город. Снег по прил. К СП 20.13330.2016.</t>
         </is>
       </c>
     </row>
@@ -2004,7 +2004,7 @@
         </is>
       </c>
       <c r="G14" t="n">
-        <v>1.5</v>
+        <v>1.35</v>
       </c>
       <c r="H14" t="inlineStr">
         <is>
@@ -2083,7 +2083,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>Контрольный город. Снег по прил. К СП 20.13330.2016. Sg уточнённое ese.pro: 1.35 кПа</t>
+          <t>Контрольный город. Снег по прил. К СП 20.13330.2016.</t>
         </is>
       </c>
     </row>
@@ -2234,7 +2234,7 @@
         </is>
       </c>
       <c r="G16" t="n">
-        <v>1</v>
+        <v>0.7</v>
       </c>
       <c r="H16" t="inlineStr">
         <is>
@@ -2313,7 +2313,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>Контрольный город. Сейсмика требует сверки по СП 14.13330. Sg уточнённое ese.pro: 0.7 кПа</t>
+          <t>Контрольный город. Сейсмика требует сверки по СП 14.13330.</t>
         </is>
       </c>
     </row>
@@ -2349,7 +2349,7 @@
         </is>
       </c>
       <c r="G17" t="n">
-        <v>2.5</v>
+        <v>2.1</v>
       </c>
       <c r="H17" t="inlineStr">
         <is>
@@ -2426,11 +2426,7 @@
           <t>verified</t>
         </is>
       </c>
-      <c r="Z17" t="inlineStr">
-        <is>
-          <t>Sg уточнённое ese.pro: 2.1 кПа</t>
-        </is>
-      </c>
+      <c r="Z17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -2464,7 +2460,7 @@
         </is>
       </c>
       <c r="G18" t="n">
-        <v>1.5</v>
+        <v>1.35</v>
       </c>
       <c r="H18" t="inlineStr">
         <is>
@@ -2541,11 +2537,7 @@
           <t>verified</t>
         </is>
       </c>
-      <c r="Z18" t="inlineStr">
-        <is>
-          <t>Sg уточнённое ese.pro: 1.35 кПа</t>
-        </is>
-      </c>
+      <c r="Z18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -2579,7 +2571,7 @@
         </is>
       </c>
       <c r="G19" t="n">
-        <v>2</v>
+        <v>1.55</v>
       </c>
       <c r="H19" t="inlineStr">
         <is>
@@ -2656,11 +2648,7 @@
           <t>verified</t>
         </is>
       </c>
-      <c r="Z19" t="inlineStr">
-        <is>
-          <t>Sg уточнённое ese.pro: 1.55 кПа</t>
-        </is>
-      </c>
+      <c r="Z19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -2805,7 +2793,7 @@
         </is>
       </c>
       <c r="G21" t="n">
-        <v>1.5</v>
+        <v>1.4</v>
       </c>
       <c r="H21" t="inlineStr">
         <is>
@@ -2882,11 +2870,7 @@
           <t>verified</t>
         </is>
       </c>
-      <c r="Z21" t="inlineStr">
-        <is>
-          <t>Sg уточнённое ese.pro: 1.4 кПа</t>
-        </is>
-      </c>
+      <c r="Z21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -2920,7 +2904,7 @@
         </is>
       </c>
       <c r="G22" t="n">
-        <v>2</v>
+        <v>1.65</v>
       </c>
       <c r="H22" t="inlineStr">
         <is>
@@ -2997,11 +2981,7 @@
           <t>verified</t>
         </is>
       </c>
-      <c r="Z22" t="inlineStr">
-        <is>
-          <t>Sg уточнённое ese.pro: 1.65 кПа</t>
-        </is>
-      </c>
+      <c r="Z22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
@@ -3035,7 +3015,7 @@
         </is>
       </c>
       <c r="G23" t="n">
-        <v>2.5</v>
+        <v>2.15</v>
       </c>
       <c r="H23" t="inlineStr">
         <is>
@@ -3112,11 +3092,7 @@
           <t>verified</t>
         </is>
       </c>
-      <c r="Z23" t="inlineStr">
-        <is>
-          <t>Sg уточнённое ese.pro: 2.15 кПа</t>
-        </is>
-      </c>
+      <c r="Z23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
@@ -3150,7 +3126,7 @@
         </is>
       </c>
       <c r="G24" t="n">
-        <v>2</v>
+        <v>1.55</v>
       </c>
       <c r="H24" t="inlineStr">
         <is>
@@ -3227,11 +3203,7 @@
           <t>verified</t>
         </is>
       </c>
-      <c r="Z24" t="inlineStr">
-        <is>
-          <t>Sg уточнённое ese.pro: 1.55 кПа</t>
-        </is>
-      </c>
+      <c r="Z24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
@@ -3265,7 +3237,7 @@
         </is>
       </c>
       <c r="G25" t="n">
-        <v>1.5</v>
+        <v>1.4</v>
       </c>
       <c r="H25" t="inlineStr">
         <is>
@@ -3342,11 +3314,7 @@
           <t>verified</t>
         </is>
       </c>
-      <c r="Z25" t="inlineStr">
-        <is>
-          <t>Sg уточнённое ese.pro: 1.4 кПа</t>
-        </is>
-      </c>
+      <c r="Z25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
@@ -3380,7 +3348,7 @@
         </is>
       </c>
       <c r="G26" t="n">
-        <v>1.5</v>
+        <v>1.05</v>
       </c>
       <c r="H26" t="inlineStr">
         <is>
@@ -3457,11 +3425,7 @@
           <t>verified</t>
         </is>
       </c>
-      <c r="Z26" t="inlineStr">
-        <is>
-          <t>Sg уточнённое ese.pro: 1.05 кПа</t>
-        </is>
-      </c>
+      <c r="Z26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
@@ -3495,7 +3459,7 @@
         </is>
       </c>
       <c r="G27" t="n">
-        <v>1.5</v>
+        <v>1.1</v>
       </c>
       <c r="H27" t="inlineStr">
         <is>
@@ -3572,11 +3536,7 @@
           <t>verified</t>
         </is>
       </c>
-      <c r="Z27" t="inlineStr">
-        <is>
-          <t>Sg уточнённое ese.pro: 1.1 кПа</t>
-        </is>
-      </c>
+      <c r="Z27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
@@ -3610,7 +3570,7 @@
         </is>
       </c>
       <c r="G28" t="n">
-        <v>2</v>
+        <v>1.8</v>
       </c>
       <c r="H28" t="inlineStr">
         <is>
@@ -3687,11 +3647,7 @@
           <t>verified</t>
         </is>
       </c>
-      <c r="Z28" t="inlineStr">
-        <is>
-          <t>Sg уточнённое ese.pro: 1.8 кПа</t>
-        </is>
-      </c>
+      <c r="Z28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
@@ -3725,7 +3681,7 @@
         </is>
       </c>
       <c r="G29" t="n">
-        <v>1</v>
+        <v>0.6</v>
       </c>
       <c r="H29" t="inlineStr">
         <is>
@@ -3802,11 +3758,7 @@
           <t>verified</t>
         </is>
       </c>
-      <c r="Z29" t="inlineStr">
-        <is>
-          <t>Sg уточнённое ese.pro: 0.6 кПа</t>
-        </is>
-      </c>
+      <c r="Z29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
@@ -3840,7 +3792,7 @@
         </is>
       </c>
       <c r="G30" t="n">
-        <v>1.5</v>
+        <v>1.25</v>
       </c>
       <c r="H30" t="inlineStr">
         <is>
@@ -3917,11 +3869,7 @@
           <t>verified</t>
         </is>
       </c>
-      <c r="Z30" t="inlineStr">
-        <is>
-          <t>Sg уточнённое ese.pro: 1.25 кПа</t>
-        </is>
-      </c>
+      <c r="Z30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
@@ -3955,7 +3903,7 @@
         </is>
       </c>
       <c r="G31" t="n">
-        <v>2</v>
+        <v>1.8</v>
       </c>
       <c r="H31" t="inlineStr">
         <is>
@@ -4032,11 +3980,7 @@
           <t>verified</t>
         </is>
       </c>
-      <c r="Z31" t="inlineStr">
-        <is>
-          <t>Sg уточнённое ese.pro: 1.8 кПа</t>
-        </is>
-      </c>
+      <c r="Z31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
@@ -4070,7 +4014,7 @@
         </is>
       </c>
       <c r="G32" t="n">
-        <v>2</v>
+        <v>1.55</v>
       </c>
       <c r="H32" t="inlineStr">
         <is>
@@ -4147,11 +4091,7 @@
           <t>verified</t>
         </is>
       </c>
-      <c r="Z32" t="inlineStr">
-        <is>
-          <t>Sg уточнённое ese.pro: 1.55 кПа</t>
-        </is>
-      </c>
+      <c r="Z32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
@@ -4185,7 +4125,7 @@
         </is>
       </c>
       <c r="G33" t="n">
-        <v>2.5</v>
+        <v>2.15</v>
       </c>
       <c r="H33" t="inlineStr">
         <is>
@@ -4262,11 +4202,7 @@
           <t>verified</t>
         </is>
       </c>
-      <c r="Z33" t="inlineStr">
-        <is>
-          <t>Sg уточнённое ese.pro: 2.15 кПа</t>
-        </is>
-      </c>
+      <c r="Z33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
@@ -4300,7 +4236,7 @@
         </is>
       </c>
       <c r="G34" t="n">
-        <v>0.5</v>
+        <v>0.4</v>
       </c>
       <c r="H34" t="inlineStr">
         <is>
@@ -4377,11 +4313,7 @@
           <t>verified</t>
         </is>
       </c>
-      <c r="Z34" t="inlineStr">
-        <is>
-          <t>Sg уточнённое ese.pro: 0.4 кПа</t>
-        </is>
-      </c>
+      <c r="Z34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
@@ -4415,7 +4347,7 @@
         </is>
       </c>
       <c r="G35" t="n">
-        <v>1.5</v>
+        <v>1.45</v>
       </c>
       <c r="H35" t="inlineStr">
         <is>
@@ -4492,11 +4424,7 @@
           <t>verified</t>
         </is>
       </c>
-      <c r="Z35" t="inlineStr">
-        <is>
-          <t>Sg уточнённое ese.pro: 1.45 кПа</t>
-        </is>
-      </c>
+      <c r="Z35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
@@ -4641,7 +4569,7 @@
         </is>
       </c>
       <c r="G37" t="n">
-        <v>2.5</v>
+        <v>2.1</v>
       </c>
       <c r="H37" t="inlineStr">
         <is>
@@ -4718,11 +4646,7 @@
           <t>verified</t>
         </is>
       </c>
-      <c r="Z37" t="inlineStr">
-        <is>
-          <t>Sg уточнённое ese.pro: 2.1 кПа</t>
-        </is>
-      </c>
+      <c r="Z37" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
@@ -4756,7 +4680,7 @@
         </is>
       </c>
       <c r="G38" t="n">
-        <v>2</v>
+        <v>1.95</v>
       </c>
       <c r="H38" t="inlineStr">
         <is>
@@ -4833,11 +4757,7 @@
           <t>verified</t>
         </is>
       </c>
-      <c r="Z38" t="inlineStr">
-        <is>
-          <t>Sg уточнённое ese.pro: 1.95 кПа</t>
-        </is>
-      </c>
+      <c r="Z38" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
@@ -4871,7 +4791,7 @@
         </is>
       </c>
       <c r="G39" t="n">
-        <v>1</v>
+        <v>0.8</v>
       </c>
       <c r="H39" t="inlineStr">
         <is>
@@ -4948,11 +4868,7 @@
           <t>verified</t>
         </is>
       </c>
-      <c r="Z39" t="inlineStr">
-        <is>
-          <t>Sg уточнённое ese.pro: 0.8 кПа</t>
-        </is>
-      </c>
+      <c r="Z39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
@@ -5097,7 +5013,7 @@
         </is>
       </c>
       <c r="G41" t="n">
-        <v>1.5</v>
+        <v>1.25</v>
       </c>
       <c r="H41" t="inlineStr">
         <is>
@@ -5174,11 +5090,7 @@
           <t>verified</t>
         </is>
       </c>
-      <c r="Z41" t="inlineStr">
-        <is>
-          <t>Sg уточнённое ese.pro: 1.25 кПа</t>
-        </is>
-      </c>
+      <c r="Z41" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
@@ -5212,7 +5124,7 @@
         </is>
       </c>
       <c r="G42" t="n">
-        <v>1</v>
+        <v>0.95</v>
       </c>
       <c r="H42" t="inlineStr">
         <is>
@@ -5289,11 +5201,7 @@
           <t>verified</t>
         </is>
       </c>
-      <c r="Z42" t="inlineStr">
-        <is>
-          <t>Sg уточнённое ese.pro: 0.95 кПа</t>
-        </is>
-      </c>
+      <c r="Z42" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
@@ -5438,7 +5346,7 @@
         </is>
       </c>
       <c r="G44" t="n">
-        <v>1.5</v>
+        <v>1.3</v>
       </c>
       <c r="H44" t="inlineStr">
         <is>
@@ -5515,11 +5423,7 @@
           <t>verified</t>
         </is>
       </c>
-      <c r="Z44" t="inlineStr">
-        <is>
-          <t>Sg уточнённое ese.pro: 1.3 кПа</t>
-        </is>
-      </c>
+      <c r="Z44" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
@@ -5553,7 +5457,7 @@
         </is>
       </c>
       <c r="G45" t="n">
-        <v>2</v>
+        <v>1.85</v>
       </c>
       <c r="H45" t="inlineStr">
         <is>
@@ -5630,11 +5534,7 @@
           <t>verified</t>
         </is>
       </c>
-      <c r="Z45" t="inlineStr">
-        <is>
-          <t>Sg уточнённое ese.pro: 1.85 кПа</t>
-        </is>
-      </c>
+      <c r="Z45" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
@@ -5668,7 +5568,7 @@
         </is>
       </c>
       <c r="G46" t="n">
-        <v>2</v>
+        <v>1.9</v>
       </c>
       <c r="H46" t="inlineStr">
         <is>
@@ -5745,11 +5645,7 @@
           <t>verified</t>
         </is>
       </c>
-      <c r="Z46" t="inlineStr">
-        <is>
-          <t>Sg уточнённое ese.pro: 1.9 кПа</t>
-        </is>
-      </c>
+      <c r="Z46" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
@@ -5783,7 +5679,7 @@
         </is>
       </c>
       <c r="G47" t="n">
-        <v>2</v>
+        <v>1.6</v>
       </c>
       <c r="H47" t="inlineStr">
         <is>
@@ -5860,11 +5756,7 @@
           <t>verified</t>
         </is>
       </c>
-      <c r="Z47" t="inlineStr">
-        <is>
-          <t>Sg уточнённое ese.pro: 1.6 кПа</t>
-        </is>
-      </c>
+      <c r="Z47" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
@@ -5898,7 +5790,7 @@
         </is>
       </c>
       <c r="G48" t="n">
-        <v>2</v>
+        <v>1.6</v>
       </c>
       <c r="H48" t="inlineStr">
         <is>
@@ -5975,11 +5867,7 @@
           <t>verified</t>
         </is>
       </c>
-      <c r="Z48" t="inlineStr">
-        <is>
-          <t>Sg уточнённое ese.pro: 1.6 кПа</t>
-        </is>
-      </c>
+      <c r="Z48" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
@@ -6013,7 +5901,7 @@
         </is>
       </c>
       <c r="G49" t="n">
-        <v>2</v>
+        <v>1.6</v>
       </c>
       <c r="H49" t="inlineStr">
         <is>
@@ -6090,11 +5978,7 @@
           <t>verified</t>
         </is>
       </c>
-      <c r="Z49" t="inlineStr">
-        <is>
-          <t>Sg уточнённое ese.pro: 1.6 кПа</t>
-        </is>
-      </c>
+      <c r="Z49" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
@@ -6128,7 +6012,7 @@
         </is>
       </c>
       <c r="G50" t="n">
-        <v>2</v>
+        <v>1.8</v>
       </c>
       <c r="H50" t="inlineStr">
         <is>
@@ -6205,11 +6089,7 @@
           <t>verified</t>
         </is>
       </c>
-      <c r="Z50" t="inlineStr">
-        <is>
-          <t>Sg уточнённое ese.pro: 1.8 кПа</t>
-        </is>
-      </c>
+      <c r="Z50" t="inlineStr"/>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
@@ -6243,7 +6123,7 @@
         </is>
       </c>
       <c r="G51" t="n">
-        <v>3.5</v>
+        <v>3.2</v>
       </c>
       <c r="H51" t="inlineStr">
         <is>
@@ -6320,11 +6200,7 @@
           <t>verified</t>
         </is>
       </c>
-      <c r="Z51" t="inlineStr">
-        <is>
-          <t>Sg уточнённое ese.pro: 3.2 кПа</t>
-        </is>
-      </c>
+      <c r="Z51" t="inlineStr"/>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
@@ -6358,7 +6234,7 @@
         </is>
       </c>
       <c r="G52" t="n">
-        <v>2</v>
+        <v>1.7</v>
       </c>
       <c r="H52" t="inlineStr">
         <is>
@@ -6435,11 +6311,7 @@
           <t>verified</t>
         </is>
       </c>
-      <c r="Z52" t="inlineStr">
-        <is>
-          <t>Sg уточнённое ese.pro: 1.7 кПа</t>
-        </is>
-      </c>
+      <c r="Z52" t="inlineStr"/>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
@@ -6473,7 +6345,7 @@
         </is>
       </c>
       <c r="G53" t="n">
-        <v>2.5</v>
+        <v>2.45</v>
       </c>
       <c r="H53" t="inlineStr">
         <is>
@@ -6550,11 +6422,7 @@
           <t>verified</t>
         </is>
       </c>
-      <c r="Z53" t="inlineStr">
-        <is>
-          <t>Sg уточнённое ese.pro: 2.45 кПа</t>
-        </is>
-      </c>
+      <c r="Z53" t="inlineStr"/>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
@@ -6588,7 +6456,7 @@
         </is>
       </c>
       <c r="G54" t="n">
-        <v>2</v>
+        <v>1.65</v>
       </c>
       <c r="H54" t="inlineStr">
         <is>
@@ -6665,11 +6533,7 @@
           <t>verified</t>
         </is>
       </c>
-      <c r="Z54" t="inlineStr">
-        <is>
-          <t>Sg уточнённое ese.pro: 1.65 кПа</t>
-        </is>
-      </c>
+      <c r="Z54" t="inlineStr"/>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
@@ -6703,7 +6567,7 @@
         </is>
       </c>
       <c r="G55" t="n">
-        <v>2</v>
+        <v>1.85</v>
       </c>
       <c r="H55" t="inlineStr">
         <is>
@@ -6780,11 +6644,7 @@
           <t>verified</t>
         </is>
       </c>
-      <c r="Z55" t="inlineStr">
-        <is>
-          <t>Sg уточнённое ese.pro: 1.85 кПа</t>
-        </is>
-      </c>
+      <c r="Z55" t="inlineStr"/>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
@@ -6818,7 +6678,7 @@
         </is>
       </c>
       <c r="G56" t="n">
-        <v>2</v>
+        <v>1.8</v>
       </c>
       <c r="H56" t="inlineStr">
         <is>
@@ -6895,11 +6755,7 @@
           <t>verified</t>
         </is>
       </c>
-      <c r="Z56" t="inlineStr">
-        <is>
-          <t>Sg уточнённое ese.pro: 1.8 кПа</t>
-        </is>
-      </c>
+      <c r="Z56" t="inlineStr"/>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
@@ -6933,7 +6789,7 @@
         </is>
       </c>
       <c r="G57" t="n">
-        <v>2</v>
+        <v>1.7</v>
       </c>
       <c r="H57" t="inlineStr">
         <is>
@@ -7010,11 +6866,7 @@
           <t>verified</t>
         </is>
       </c>
-      <c r="Z57" t="inlineStr">
-        <is>
-          <t>Sg уточнённое ese.pro: 1.7 кПа</t>
-        </is>
-      </c>
+      <c r="Z57" t="inlineStr"/>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
@@ -7159,7 +7011,7 @@
         </is>
       </c>
       <c r="G59" t="n">
-        <v>2</v>
+        <v>1.55</v>
       </c>
       <c r="H59" t="inlineStr">
         <is>
@@ -7236,11 +7088,7 @@
           <t>verified</t>
         </is>
       </c>
-      <c r="Z59" t="inlineStr">
-        <is>
-          <t>Sg уточнённое ese.pro: 1.55 кПа</t>
-        </is>
-      </c>
+      <c r="Z59" t="inlineStr"/>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
@@ -7274,7 +7122,7 @@
         </is>
       </c>
       <c r="G60" t="n">
-        <v>1.5</v>
+        <v>1.4</v>
       </c>
       <c r="H60" t="inlineStr">
         <is>
@@ -7351,11 +7199,7 @@
           <t>verified</t>
         </is>
       </c>
-      <c r="Z60" t="inlineStr">
-        <is>
-          <t>Sg уточнённое ese.pro: 1.4 кПа</t>
-        </is>
-      </c>
+      <c r="Z60" t="inlineStr"/>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
@@ -7389,7 +7233,7 @@
         </is>
       </c>
       <c r="G61" t="n">
-        <v>2</v>
+        <v>1.6</v>
       </c>
       <c r="H61" t="inlineStr">
         <is>
@@ -7466,11 +7310,7 @@
           <t>verified</t>
         </is>
       </c>
-      <c r="Z61" t="inlineStr">
-        <is>
-          <t>Sg уточнённое ese.pro: 1.6 кПа</t>
-        </is>
-      </c>
+      <c r="Z61" t="inlineStr"/>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
@@ -7504,7 +7344,7 @@
         </is>
       </c>
       <c r="G62" t="n">
-        <v>2</v>
+        <v>1.8</v>
       </c>
       <c r="H62" t="inlineStr">
         <is>
@@ -7581,11 +7421,7 @@
           <t>verified</t>
         </is>
       </c>
-      <c r="Z62" t="inlineStr">
-        <is>
-          <t>Sg уточнённое ese.pro: 1.8 кПа</t>
-        </is>
-      </c>
+      <c r="Z62" t="inlineStr"/>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
@@ -7619,7 +7455,7 @@
         </is>
       </c>
       <c r="G63" t="n">
-        <v>2.5</v>
+        <v>2.25</v>
       </c>
       <c r="H63" t="inlineStr">
         <is>
@@ -7696,11 +7532,7 @@
           <t>verified</t>
         </is>
       </c>
-      <c r="Z63" t="inlineStr">
-        <is>
-          <t>Sg уточнённое ese.pro: 2.25 кПа</t>
-        </is>
-      </c>
+      <c r="Z63" t="inlineStr"/>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
@@ -7734,7 +7566,7 @@
         </is>
       </c>
       <c r="G64" t="n">
-        <v>1.5</v>
+        <v>1.3</v>
       </c>
       <c r="H64" t="inlineStr">
         <is>
@@ -7811,11 +7643,7 @@
           <t>verified</t>
         </is>
       </c>
-      <c r="Z64" t="inlineStr">
-        <is>
-          <t>Sg уточнённое ese.pro: 1.3 кПа</t>
-        </is>
-      </c>
+      <c r="Z64" t="inlineStr"/>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
@@ -7960,7 +7788,7 @@
         </is>
       </c>
       <c r="G66" t="n">
-        <v>2</v>
+        <v>1.8</v>
       </c>
       <c r="H66" t="inlineStr">
         <is>
@@ -8037,11 +7865,7 @@
           <t>verified</t>
         </is>
       </c>
-      <c r="Z66" t="inlineStr">
-        <is>
-          <t>Sg уточнённое ese.pro: 1.8 кПа</t>
-        </is>
-      </c>
+      <c r="Z66" t="inlineStr"/>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
@@ -8075,7 +7899,7 @@
         </is>
       </c>
       <c r="G67" t="n">
-        <v>2</v>
+        <v>1.95</v>
       </c>
       <c r="H67" t="inlineStr">
         <is>
@@ -8152,11 +7976,7 @@
           <t>verified</t>
         </is>
       </c>
-      <c r="Z67" t="inlineStr">
-        <is>
-          <t>Sg уточнённое ese.pro: 1.95 кПа</t>
-        </is>
-      </c>
+      <c r="Z67" t="inlineStr"/>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
@@ -8301,7 +8121,7 @@
         </is>
       </c>
       <c r="G69" t="n">
-        <v>3</v>
+        <v>2.55</v>
       </c>
       <c r="H69" t="inlineStr">
         <is>
@@ -8378,11 +8198,7 @@
           <t>verified</t>
         </is>
       </c>
-      <c r="Z69" t="inlineStr">
-        <is>
-          <t>Sg уточнённое ese.pro: 2.55 кПа</t>
-        </is>
-      </c>
+      <c r="Z69" t="inlineStr"/>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
@@ -8527,7 +8343,7 @@
         </is>
       </c>
       <c r="G71" t="n">
-        <v>2</v>
+        <v>1.8</v>
       </c>
       <c r="H71" t="inlineStr">
         <is>
@@ -8604,11 +8420,7 @@
           <t>verified</t>
         </is>
       </c>
-      <c r="Z71" t="inlineStr">
-        <is>
-          <t>Sg уточнённое ese.pro: 1.8 кПа</t>
-        </is>
-      </c>
+      <c r="Z71" t="inlineStr"/>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
@@ -8864,7 +8676,7 @@
         </is>
       </c>
       <c r="G74" t="n">
-        <v>2</v>
+        <v>1.9</v>
       </c>
       <c r="H74" t="inlineStr">
         <is>
@@ -8941,11 +8753,7 @@
           <t>verified</t>
         </is>
       </c>
-      <c r="Z74" t="inlineStr">
-        <is>
-          <t>Sg уточнённое ese.pro: 1.9 кПа</t>
-        </is>
-      </c>
+      <c r="Z74" t="inlineStr"/>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
@@ -8979,7 +8787,7 @@
         </is>
       </c>
       <c r="G75" t="n">
-        <v>0.5</v>
+        <v>0.4</v>
       </c>
       <c r="H75" t="inlineStr">
         <is>
@@ -9056,11 +8864,7 @@
           <t>verified</t>
         </is>
       </c>
-      <c r="Z75" t="inlineStr">
-        <is>
-          <t>Sg уточнённое ese.pro: 0.4 кПа</t>
-        </is>
-      </c>
+      <c r="Z75" t="inlineStr"/>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
@@ -9205,7 +9009,7 @@
         </is>
       </c>
       <c r="G77" t="n">
-        <v>1</v>
+        <v>0.95</v>
       </c>
       <c r="H77" t="inlineStr">
         <is>
@@ -9282,11 +9086,7 @@
           <t>verified</t>
         </is>
       </c>
-      <c r="Z77" t="inlineStr">
-        <is>
-          <t>Sg уточнённое ese.pro: 0.95 кПа</t>
-        </is>
-      </c>
+      <c r="Z77" t="inlineStr"/>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
@@ -9320,7 +9120,7 @@
         </is>
       </c>
       <c r="G78" t="n">
-        <v>4</v>
+        <v>3.85</v>
       </c>
       <c r="H78" t="inlineStr">
         <is>
@@ -9397,11 +9197,7 @@
           <t>verified</t>
         </is>
       </c>
-      <c r="Z78" t="inlineStr">
-        <is>
-          <t>Sg уточнённое ese.pro: 3.85 кПа</t>
-        </is>
-      </c>
+      <c r="Z78" t="inlineStr"/>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
@@ -9435,7 +9231,7 @@
         </is>
       </c>
       <c r="G79" t="n">
-        <v>4</v>
+        <v>4.1</v>
       </c>
       <c r="H79" t="inlineStr">
         <is>
@@ -9512,11 +9308,7 @@
           <t>verified</t>
         </is>
       </c>
-      <c r="Z79" t="inlineStr">
-        <is>
-          <t>Sg уточнённое ese.pro: 4.1 кПа</t>
-        </is>
-      </c>
+      <c r="Z79" t="inlineStr"/>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
@@ -9661,7 +9453,7 @@
         </is>
       </c>
       <c r="G81" t="n">
-        <v>1.5</v>
+        <v>1.35</v>
       </c>
       <c r="H81" t="inlineStr">
         <is>
@@ -9738,11 +9530,7 @@
           <t>verified</t>
         </is>
       </c>
-      <c r="Z81" t="inlineStr">
-        <is>
-          <t>Sg уточнённое ese.pro: 1.35 кПа</t>
-        </is>
-      </c>
+      <c r="Z81" t="inlineStr"/>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
@@ -9887,7 +9675,7 @@
         </is>
       </c>
       <c r="G83" t="n">
-        <v>1</v>
+        <v>0.65</v>
       </c>
       <c r="H83" t="inlineStr">
         <is>
@@ -9964,11 +9752,7 @@
           <t>verified</t>
         </is>
       </c>
-      <c r="Z83" t="inlineStr">
-        <is>
-          <t>Sg уточнённое ese.pro: 0.65 кПа</t>
-        </is>
-      </c>
+      <c r="Z83" t="inlineStr"/>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
@@ -10002,7 +9786,7 @@
         </is>
       </c>
       <c r="G84" t="n">
-        <v>1</v>
+        <v>0.6</v>
       </c>
       <c r="H84" t="inlineStr">
         <is>
@@ -10079,11 +9863,7 @@
           <t>verified</t>
         </is>
       </c>
-      <c r="Z84" t="inlineStr">
-        <is>
-          <t>Sg уточнённое ese.pro: 0.6 кПа</t>
-        </is>
-      </c>
+      <c r="Z84" t="inlineStr"/>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
@@ -10117,7 +9897,7 @@
         </is>
       </c>
       <c r="G85" t="n">
-        <v>0.5</v>
+        <v>0.45</v>
       </c>
       <c r="H85" t="inlineStr">
         <is>
@@ -10194,11 +9974,7 @@
           <t>verified</t>
         </is>
       </c>
-      <c r="Z85" t="inlineStr">
-        <is>
-          <t>Sg уточнённое ese.pro: 0.45 кПа</t>
-        </is>
-      </c>
+      <c r="Z85" t="inlineStr"/>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
@@ -10343,7 +10119,7 @@
         </is>
       </c>
       <c r="G87" t="n">
-        <v>1</v>
+        <v>0.7</v>
       </c>
       <c r="H87" t="inlineStr">
         <is>
@@ -10420,11 +10196,7 @@
           <t>verified</t>
         </is>
       </c>
-      <c r="Z87" t="inlineStr">
-        <is>
-          <t>Sg уточнённое ese.pro: 0.7 кПа</t>
-        </is>
-      </c>
+      <c r="Z87" t="inlineStr"/>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
@@ -10458,7 +10230,7 @@
         </is>
       </c>
       <c r="G88" t="n">
-        <v>1</v>
+        <v>0.9</v>
       </c>
       <c r="H88" t="inlineStr">
         <is>
@@ -10535,11 +10307,7 @@
           <t>verified</t>
         </is>
       </c>
-      <c r="Z88" t="inlineStr">
-        <is>
-          <t>Sg уточнённое ese.pro: 0.9 кПа</t>
-        </is>
-      </c>
+      <c r="Z88" t="inlineStr"/>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
@@ -10906,7 +10674,7 @@
         </is>
       </c>
       <c r="G92" t="n">
-        <v>1</v>
+        <v>0.85</v>
       </c>
       <c r="H92" t="inlineStr">
         <is>
@@ -10983,11 +10751,7 @@
           <t>verified</t>
         </is>
       </c>
-      <c r="Z92" t="inlineStr">
-        <is>
-          <t>Sg уточнённое ese.pro: 0.85 кПа</t>
-        </is>
-      </c>
+      <c r="Z92" t="inlineStr"/>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
@@ -11021,7 +10785,7 @@
         </is>
       </c>
       <c r="G93" t="n">
-        <v>2.5</v>
+        <v>2.3</v>
       </c>
       <c r="H93" t="inlineStr">
         <is>
@@ -11098,11 +10862,7 @@
           <t>verified</t>
         </is>
       </c>
-      <c r="Z93" t="inlineStr">
-        <is>
-          <t>Sg уточнённое ese.pro: 2.3 кПа</t>
-        </is>
-      </c>
+      <c r="Z93" t="inlineStr"/>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
@@ -11136,7 +10896,7 @@
         </is>
       </c>
       <c r="G94" t="n">
-        <v>1.5</v>
+        <v>1.25</v>
       </c>
       <c r="H94" t="inlineStr">
         <is>
@@ -11213,11 +10973,7 @@
           <t>verified</t>
         </is>
       </c>
-      <c r="Z94" t="inlineStr">
-        <is>
-          <t>Sg уточнённое ese.pro: 1.25 кПа</t>
-        </is>
-      </c>
+      <c r="Z94" t="inlineStr"/>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
@@ -11251,7 +11007,7 @@
         </is>
       </c>
       <c r="G95" t="n">
-        <v>1.5</v>
+        <v>1.25</v>
       </c>
       <c r="H95" t="inlineStr">
         <is>
@@ -11328,11 +11084,7 @@
           <t>verified</t>
         </is>
       </c>
-      <c r="Z95" t="inlineStr">
-        <is>
-          <t>Sg уточнённое ese.pro: 1.25 кПа</t>
-        </is>
-      </c>
+      <c r="Z95" t="inlineStr"/>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
@@ -11366,7 +11118,7 @@
         </is>
       </c>
       <c r="G96" t="n">
-        <v>1</v>
+        <v>0.7</v>
       </c>
       <c r="H96" t="inlineStr">
         <is>
@@ -11443,11 +11195,7 @@
           <t>verified</t>
         </is>
       </c>
-      <c r="Z96" t="inlineStr">
-        <is>
-          <t>Sg уточнённое ese.pro: 0.7 кПа</t>
-        </is>
-      </c>
+      <c r="Z96" t="inlineStr"/>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
@@ -11592,7 +11340,7 @@
         </is>
       </c>
       <c r="G98" t="n">
-        <v>2.5</v>
+        <v>2.45</v>
       </c>
       <c r="H98" t="inlineStr">
         <is>
@@ -11669,11 +11417,7 @@
           <t>verified</t>
         </is>
       </c>
-      <c r="Z98" t="inlineStr">
-        <is>
-          <t>Sg уточнённое ese.pro: 2.45 кПа</t>
-        </is>
-      </c>
+      <c r="Z98" t="inlineStr"/>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
@@ -11707,7 +11451,7 @@
         </is>
       </c>
       <c r="G99" t="n">
-        <v>2</v>
+        <v>1.85</v>
       </c>
       <c r="H99" t="inlineStr">
         <is>
@@ -11784,11 +11528,7 @@
           <t>verified</t>
         </is>
       </c>
-      <c r="Z99" t="inlineStr">
-        <is>
-          <t>Sg уточнённое ese.pro: 1.85 кПа</t>
-        </is>
-      </c>
+      <c r="Z99" t="inlineStr"/>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
@@ -11822,7 +11562,7 @@
         </is>
       </c>
       <c r="G100" t="n">
-        <v>1.5</v>
+        <v>1.1</v>
       </c>
       <c r="H100" t="inlineStr">
         <is>
@@ -11899,11 +11639,7 @@
           <t>verified</t>
         </is>
       </c>
-      <c r="Z100" t="inlineStr">
-        <is>
-          <t>Sg уточнённое ese.pro: 1.1 кПа</t>
-        </is>
-      </c>
+      <c r="Z100" t="inlineStr"/>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
@@ -11937,7 +11673,7 @@
         </is>
       </c>
       <c r="G101" t="n">
-        <v>1.5</v>
+        <v>1.2</v>
       </c>
       <c r="H101" t="inlineStr">
         <is>
@@ -12014,11 +11750,7 @@
           <t>verified</t>
         </is>
       </c>
-      <c r="Z101" t="inlineStr">
-        <is>
-          <t>Sg уточнённое ese.pro: 1.2 кПа</t>
-        </is>
-      </c>
+      <c r="Z101" t="inlineStr"/>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
@@ -12052,7 +11784,7 @@
         </is>
       </c>
       <c r="G102" t="n">
-        <v>1.5</v>
+        <v>1.25</v>
       </c>
       <c r="H102" t="inlineStr">
         <is>
@@ -12129,11 +11861,7 @@
           <t>verified</t>
         </is>
       </c>
-      <c r="Z102" t="inlineStr">
-        <is>
-          <t>Sg уточнённое ese.pro: 1.25 кПа</t>
-        </is>
-      </c>
+      <c r="Z102" t="inlineStr"/>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
@@ -12167,7 +11895,7 @@
         </is>
       </c>
       <c r="G103" t="n">
-        <v>1.5</v>
+        <v>1.4</v>
       </c>
       <c r="H103" t="inlineStr">
         <is>
@@ -12244,11 +11972,7 @@
           <t>verified</t>
         </is>
       </c>
-      <c r="Z103" t="inlineStr">
-        <is>
-          <t>Sg уточнённое ese.pro: 1.4 кПа</t>
-        </is>
-      </c>
+      <c r="Z103" t="inlineStr"/>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
@@ -12282,7 +12006,7 @@
         </is>
       </c>
       <c r="G104" t="n">
-        <v>2</v>
+        <v>1.55</v>
       </c>
       <c r="H104" t="inlineStr">
         <is>
@@ -12359,11 +12083,7 @@
           <t>verified</t>
         </is>
       </c>
-      <c r="Z104" t="inlineStr">
-        <is>
-          <t>Sg уточнённое ese.pro: 1.55 кПа</t>
-        </is>
-      </c>
+      <c r="Z104" t="inlineStr"/>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
@@ -12397,7 +12117,7 @@
         </is>
       </c>
       <c r="G105" t="n">
-        <v>2</v>
+        <v>1.8</v>
       </c>
       <c r="H105" t="inlineStr">
         <is>
@@ -12474,11 +12194,7 @@
           <t>verified</t>
         </is>
       </c>
-      <c r="Z105" t="inlineStr">
-        <is>
-          <t>Sg уточнённое ese.pro: 1.8 кПа</t>
-        </is>
-      </c>
+      <c r="Z105" t="inlineStr"/>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
@@ -12512,7 +12228,7 @@
         </is>
       </c>
       <c r="G106" t="n">
-        <v>2.5</v>
+        <v>2.4</v>
       </c>
       <c r="H106" t="inlineStr">
         <is>
@@ -12589,11 +12305,7 @@
           <t>verified</t>
         </is>
       </c>
-      <c r="Z106" t="inlineStr">
-        <is>
-          <t>Sg уточнённое ese.pro: 2.4 кПа</t>
-        </is>
-      </c>
+      <c r="Z106" t="inlineStr"/>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
@@ -12738,7 +12450,7 @@
         </is>
       </c>
       <c r="G108" t="n">
-        <v>1.5</v>
+        <v>1.25</v>
       </c>
       <c r="H108" t="inlineStr">
         <is>
@@ -12815,11 +12527,7 @@
           <t>verified</t>
         </is>
       </c>
-      <c r="Z108" t="inlineStr">
-        <is>
-          <t>Sg уточнённое ese.pro: 1.25 кПа</t>
-        </is>
-      </c>
+      <c r="Z108" t="inlineStr"/>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
@@ -12853,7 +12561,7 @@
         </is>
       </c>
       <c r="G109" t="n">
-        <v>1.5</v>
+        <v>1.1</v>
       </c>
       <c r="H109" t="inlineStr">
         <is>
@@ -12930,11 +12638,7 @@
           <t>verified</t>
         </is>
       </c>
-      <c r="Z109" t="inlineStr">
-        <is>
-          <t>Sg уточнённое ese.pro: 1.1 кПа</t>
-        </is>
-      </c>
+      <c r="Z109" t="inlineStr"/>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
@@ -12968,7 +12672,7 @@
         </is>
       </c>
       <c r="G110" t="n">
-        <v>1.5</v>
+        <v>1.05</v>
       </c>
       <c r="H110" t="inlineStr">
         <is>
@@ -13045,11 +12749,7 @@
           <t>verified</t>
         </is>
       </c>
-      <c r="Z110" t="inlineStr">
-        <is>
-          <t>Sg уточнённое ese.pro: 1.05 кПа</t>
-        </is>
-      </c>
+      <c r="Z110" t="inlineStr"/>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
@@ -13083,7 +12783,7 @@
         </is>
       </c>
       <c r="G111" t="n">
-        <v>1.5</v>
+        <v>1.25</v>
       </c>
       <c r="H111" t="inlineStr">
         <is>
@@ -13160,11 +12860,7 @@
           <t>verified</t>
         </is>
       </c>
-      <c r="Z111" t="inlineStr">
-        <is>
-          <t>Sg уточнённое ese.pro: 1.25 кПа</t>
-        </is>
-      </c>
+      <c r="Z111" t="inlineStr"/>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
@@ -13198,7 +12894,7 @@
         </is>
       </c>
       <c r="G112" t="n">
-        <v>2.5</v>
+        <v>2.25</v>
       </c>
       <c r="H112" t="inlineStr">
         <is>
@@ -13275,11 +12971,7 @@
           <t>verified</t>
         </is>
       </c>
-      <c r="Z112" t="inlineStr">
-        <is>
-          <t>Sg уточнённое ese.pro: 2.25 кПа</t>
-        </is>
-      </c>
+      <c r="Z112" t="inlineStr"/>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
@@ -13535,7 +13227,7 @@
         </is>
       </c>
       <c r="G115" t="n">
-        <v>2.5</v>
+        <v>2.15</v>
       </c>
       <c r="H115" t="inlineStr">
         <is>
@@ -13612,11 +13304,7 @@
           <t>verified</t>
         </is>
       </c>
-      <c r="Z115" t="inlineStr">
-        <is>
-          <t>Sg уточнённое ese.pro: 2.15 кПа</t>
-        </is>
-      </c>
+      <c r="Z115" t="inlineStr"/>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
@@ -13650,7 +13338,7 @@
         </is>
       </c>
       <c r="G116" t="n">
-        <v>1.5</v>
+        <v>1.3</v>
       </c>
       <c r="H116" t="inlineStr">
         <is>
@@ -13727,11 +13415,7 @@
           <t>verified</t>
         </is>
       </c>
-      <c r="Z116" t="inlineStr">
-        <is>
-          <t>Sg уточнённое ese.pro: 1.3 кПа</t>
-        </is>
-      </c>
+      <c r="Z116" t="inlineStr"/>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
@@ -13765,7 +13449,7 @@
         </is>
       </c>
       <c r="G117" t="n">
-        <v>2</v>
+        <v>1.55</v>
       </c>
       <c r="H117" t="inlineStr">
         <is>
@@ -13842,11 +13526,7 @@
           <t>verified</t>
         </is>
       </c>
-      <c r="Z117" t="inlineStr">
-        <is>
-          <t>Sg уточнённое ese.pro: 1.55 кПа</t>
-        </is>
-      </c>
+      <c r="Z117" t="inlineStr"/>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
@@ -13880,7 +13560,7 @@
         </is>
       </c>
       <c r="G118" t="n">
-        <v>2</v>
+        <v>1.8</v>
       </c>
       <c r="H118" t="inlineStr">
         <is>
@@ -13957,11 +13637,7 @@
           <t>verified</t>
         </is>
       </c>
-      <c r="Z118" t="inlineStr">
-        <is>
-          <t>Sg уточнённое ese.pro: 1.8 кПа</t>
-        </is>
-      </c>
+      <c r="Z118" t="inlineStr"/>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
@@ -13995,7 +13671,7 @@
         </is>
       </c>
       <c r="G119" t="n">
-        <v>1.5</v>
+        <v>1.4</v>
       </c>
       <c r="H119" t="inlineStr">
         <is>
@@ -14072,11 +13748,7 @@
           <t>verified</t>
         </is>
       </c>
-      <c r="Z119" t="inlineStr">
-        <is>
-          <t>Sg уточнённое ese.pro: 1.4 кПа</t>
-        </is>
-      </c>
+      <c r="Z119" t="inlineStr"/>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
@@ -14887,7 +14559,7 @@
         </is>
       </c>
       <c r="G127" t="n">
-        <v>1.5</v>
+        <v>1.45</v>
       </c>
       <c r="H127" t="inlineStr">
         <is>
@@ -14964,11 +14636,7 @@
           <t>verified</t>
         </is>
       </c>
-      <c r="Z127" t="inlineStr">
-        <is>
-          <t>Sg уточнённое ese.pro: 1.45 кПа</t>
-        </is>
-      </c>
+      <c r="Z127" t="inlineStr"/>
     </row>
     <row r="128">
       <c r="A128" t="inlineStr">
@@ -15890,7 +15558,7 @@
         </is>
       </c>
       <c r="G136" t="n">
-        <v>1.5</v>
+        <v>1.45</v>
       </c>
       <c r="H136" t="inlineStr">
         <is>
@@ -15967,11 +15635,7 @@
           <t>verified</t>
         </is>
       </c>
-      <c r="Z136" t="inlineStr">
-        <is>
-          <t>Sg уточнённое ese.pro: 1.45 кПа</t>
-        </is>
-      </c>
+      <c r="Z136" t="inlineStr"/>
     </row>
     <row r="137">
       <c r="A137" t="inlineStr">
@@ -16005,7 +15669,7 @@
         </is>
       </c>
       <c r="G137" t="n">
-        <v>2</v>
+        <v>1.6</v>
       </c>
       <c r="H137" t="inlineStr">
         <is>
@@ -16082,11 +15746,7 @@
           <t>verified</t>
         </is>
       </c>
-      <c r="Z137" t="inlineStr">
-        <is>
-          <t>Sg уточнённое ese.pro: 1.6 кПа</t>
-        </is>
-      </c>
+      <c r="Z137" t="inlineStr"/>
     </row>
     <row r="138">
       <c r="A138" t="inlineStr">
@@ -17008,7 +16668,7 @@
         </is>
       </c>
       <c r="G146" t="n">
-        <v>1.5</v>
+        <v>1.1</v>
       </c>
       <c r="H146" t="inlineStr">
         <is>
@@ -17085,11 +16745,7 @@
           <t>verified</t>
         </is>
       </c>
-      <c r="Z146" t="inlineStr">
-        <is>
-          <t>Sg уточнённое ese.pro: 1.1 кПа</t>
-        </is>
-      </c>
+      <c r="Z146" t="inlineStr"/>
     </row>
     <row r="147">
       <c r="A147" t="inlineStr">
@@ -17900,7 +17556,7 @@
         </is>
       </c>
       <c r="G154" t="n">
-        <v>2</v>
+        <v>1.55</v>
       </c>
       <c r="H154" t="inlineStr">
         <is>
@@ -17977,11 +17633,7 @@
           <t>verified</t>
         </is>
       </c>
-      <c r="Z154" t="inlineStr">
-        <is>
-          <t>Sg уточнённое ese.pro: 1.55 кПа</t>
-        </is>
-      </c>
+      <c r="Z154" t="inlineStr"/>
     </row>
     <row r="155">
       <c r="A155" t="inlineStr">
@@ -18015,7 +17667,7 @@
         </is>
       </c>
       <c r="G155" t="n">
-        <v>2</v>
+        <v>1.6</v>
       </c>
       <c r="H155" t="inlineStr">
         <is>
@@ -18092,11 +17744,7 @@
           <t>verified</t>
         </is>
       </c>
-      <c r="Z155" t="inlineStr">
-        <is>
-          <t>Sg уточнённое ese.pro: 1.6 кПа</t>
-        </is>
-      </c>
+      <c r="Z155" t="inlineStr"/>
     </row>
     <row r="156">
       <c r="A156" t="inlineStr">
@@ -21793,7 +21441,7 @@
         </is>
       </c>
       <c r="G189" t="n">
-        <v>1.5</v>
+        <v>1.4</v>
       </c>
       <c r="H189" t="inlineStr">
         <is>
@@ -21870,11 +21518,7 @@
           <t>verified</t>
         </is>
       </c>
-      <c r="Z189" t="inlineStr">
-        <is>
-          <t>Sg уточнённое ese.pro: 1.4 кПа</t>
-        </is>
-      </c>
+      <c r="Z189" t="inlineStr"/>
     </row>
     <row r="190">
       <c r="A190" t="inlineStr">
@@ -23684,7 +23328,7 @@
         </is>
       </c>
       <c r="G206" t="n">
-        <v>2</v>
+        <v>1.6</v>
       </c>
       <c r="H206" t="inlineStr">
         <is>
@@ -23761,11 +23405,7 @@
           <t>verified</t>
         </is>
       </c>
-      <c r="Z206" t="inlineStr">
-        <is>
-          <t>Sg уточнённое ese.pro: 1.6 кПа</t>
-        </is>
-      </c>
+      <c r="Z206" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -24373,7 +24013,7 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>1.5</v>
+        <v>1.45</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
@@ -24422,7 +24062,7 @@
         </is>
       </c>
       <c r="D3" t="n">
-        <v>1.5</v>
+        <v>1.3</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
@@ -24450,7 +24090,7 @@
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>Контрольный город. Снег по прил. К СП 20.13330.2016. Sg уточнённое ese.pro: 1.3 кПа</t>
+          <t>Контрольный город. Снег по прил. К СП 20.13330.2016.</t>
         </is>
       </c>
     </row>
@@ -24471,7 +24111,7 @@
         </is>
       </c>
       <c r="D4" t="n">
-        <v>1.5</v>
+        <v>1.2</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
@@ -24499,7 +24139,7 @@
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>Контрольный город. Базовая запись из ТЗ. Sg уточнённое ese.pro: 1.2 кПа</t>
+          <t>Контрольный город. Базовая запись из ТЗ.</t>
         </is>
       </c>
     </row>
@@ -24520,7 +24160,7 @@
         </is>
       </c>
       <c r="D5" t="n">
-        <v>1.5</v>
+        <v>1.35</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
@@ -24548,7 +24188,7 @@
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>Контрольный город. Снег по прил. К СП 20.13330.2016. Sg уточнённое ese.pro: 1.35 кПа</t>
+          <t>Контрольный город. Снег по прил. К СП 20.13330.2016.</t>
         </is>
       </c>
     </row>
@@ -24569,7 +24209,7 @@
         </is>
       </c>
       <c r="D6" t="n">
-        <v>2.5</v>
+        <v>2.3</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
@@ -24597,7 +24237,7 @@
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>Контрольный город. Снег по прил. К СП 20.13330.2016. Sg уточнённое ese.pro: 2.3 кПа</t>
+          <t>Контрольный город. Снег по прил. К СП 20.13330.2016.</t>
         </is>
       </c>
     </row>
@@ -24618,7 +24258,7 @@
         </is>
       </c>
       <c r="D7" t="n">
-        <v>2</v>
+        <v>1.6</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
@@ -24646,7 +24286,7 @@
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>Контрольный город. Снег по прил. К СП 20.13330.2016. Sg уточнённое ese.pro: 1.6 кПа</t>
+          <t>Контрольный город. Снег по прил. К СП 20.13330.2016.</t>
         </is>
       </c>
     </row>
@@ -24667,7 +24307,7 @@
         </is>
       </c>
       <c r="D8" t="n">
-        <v>1.5</v>
+        <v>1.1</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
@@ -24695,7 +24335,7 @@
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>Контрольный город. Снег по прил. К СП 20.13330.2016. Sg уточнённое ese.pro: 1.1 кПа</t>
+          <t>Контрольный город. Снег по прил. К СП 20.13330.2016.</t>
         </is>
       </c>
     </row>
@@ -24716,7 +24356,7 @@
         </is>
       </c>
       <c r="D9" t="n">
-        <v>2</v>
+        <v>1.95</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
@@ -24744,7 +24384,7 @@
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>Контрольный город. Снег по прил. К СП 20.13330.2016. Sg уточнённое ese.pro: 1.95 кПа</t>
+          <t>Контрольный город. Снег по прил. К СП 20.13330.2016.</t>
         </is>
       </c>
     </row>
@@ -24765,7 +24405,7 @@
         </is>
       </c>
       <c r="D10" t="n">
-        <v>2.5</v>
+        <v>2.45</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
@@ -24793,7 +24433,7 @@
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>Контрольный город. Снег по прил. К СП 20.13330.2016 — требует сверки (граница IV/V). Sg уточнённое ese.pro: 2.45 кПа</t>
+          <t>Контрольный город. Снег по прил. К СП 20.13330.2016 — требует сверки (граница IV/V).</t>
         </is>
       </c>
     </row>
@@ -24814,7 +24454,7 @@
         </is>
       </c>
       <c r="D11" t="n">
-        <v>2</v>
+        <v>1.6</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
@@ -24842,7 +24482,7 @@
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>Контрольный город. Снег по прил. К СП 20.13330.2016. Sg уточнённое ese.pro: 1.6 кПа</t>
+          <t>Контрольный город. Снег по прил. К СП 20.13330.2016.</t>
         </is>
       </c>
     </row>
@@ -24863,7 +24503,7 @@
         </is>
       </c>
       <c r="D12" t="n">
-        <v>1</v>
+        <v>0.85</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
@@ -24891,7 +24531,7 @@
       </c>
       <c r="K12" t="inlineStr">
         <is>
-          <t>Контрольный город. Снег по прил. К СП 20.13330.2016. Sg уточнённое ese.pro: 0.85 кПа</t>
+          <t>Контрольный город. Снег по прил. К СП 20.13330.2016.</t>
         </is>
       </c>
     </row>
@@ -24912,7 +24552,7 @@
         </is>
       </c>
       <c r="D13" t="n">
-        <v>2</v>
+        <v>1.6</v>
       </c>
       <c r="E13" t="inlineStr">
         <is>
@@ -24940,7 +24580,7 @@
       </c>
       <c r="K13" t="inlineStr">
         <is>
-          <t>Контрольный город. Снег по прил. К СП 20.13330.2016. Sg уточнённое ese.pro: 1.6 кПа</t>
+          <t>Контрольный город. Снег по прил. К СП 20.13330.2016.</t>
         </is>
       </c>
     </row>
@@ -24961,7 +24601,7 @@
         </is>
       </c>
       <c r="D14" t="n">
-        <v>1.5</v>
+        <v>1.35</v>
       </c>
       <c r="E14" t="inlineStr">
         <is>
@@ -24989,7 +24629,7 @@
       </c>
       <c r="K14" t="inlineStr">
         <is>
-          <t>Контрольный город. Снег по прил. К СП 20.13330.2016. Sg уточнённое ese.pro: 1.35 кПа</t>
+          <t>Контрольный город. Снег по прил. К СП 20.13330.2016.</t>
         </is>
       </c>
     </row>
@@ -25059,7 +24699,7 @@
         </is>
       </c>
       <c r="D16" t="n">
-        <v>1</v>
+        <v>0.7</v>
       </c>
       <c r="E16" t="inlineStr">
         <is>
@@ -25087,7 +24727,7 @@
       </c>
       <c r="K16" t="inlineStr">
         <is>
-          <t>Контрольный город. Сейсмика требует сверки по СП 14.13330. Sg уточнённое ese.pro: 0.7 кПа</t>
+          <t>Контрольный город. Сейсмика требует сверки по СП 14.13330.</t>
         </is>
       </c>
     </row>
